--- a/reports/Debug-snowbowl-20251230/For The Day (Prior Year)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20251230/For The Day (Prior Year)_Visits.xlsx
@@ -34,13 +34,13 @@
     <t>Snowbowl Passes</t>
   </si>
   <si>
+    <t>Snowbowl Uplift Tickets</t>
+  </si>
+  <si>
     <t>Snowbowl Tickets</t>
   </si>
   <si>
     <t>Snowbowl Comp Tickets</t>
-  </si>
-  <si>
-    <t>Snowbowl Uplift Tickets</t>
   </si>
 </sst>
 </file>
@@ -434,7 +434,7 @@
         <v>45657</v>
       </c>
       <c r="C2" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,10 +448,10 @@
         <v>45657</v>
       </c>
       <c r="C3" s="2">
-        <v>58</v>
+        <v>266</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -462,10 +462,10 @@
         <v>45657</v>
       </c>
       <c r="C4" s="2">
-        <v>471</v>
+        <v>1496</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -490,10 +490,10 @@
         <v>45657</v>
       </c>
       <c r="C6" s="2">
-        <v>1496</v>
+        <v>490</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -504,10 +504,10 @@
         <v>45657</v>
       </c>
       <c r="C7" s="2">
-        <v>490</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -518,10 +518,10 @@
         <v>45657</v>
       </c>
       <c r="C8" s="2">
-        <v>266</v>
+        <v>58</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -532,7 +532,7 @@
         <v>45657</v>
       </c>
       <c r="C9" s="2">
-        <v>8</v>
+        <v>471</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>5</v>
